--- a/astro-site/public/dl/how-to-open-a-pastry-shop/startup-cost-calculator.xlsx
+++ b/astro-site/public/dl/how-to-open-a-pastry-shop/startup-cost-calculator.xlsx
@@ -2135,7 +2135,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Planetary mixer, 20 qt</t>
+          <t>Planetary mixer, 20 L (about 21 qt)</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
